--- a/backend/uploads/Form4_EndOfTerm1_2026.xlsx
+++ b/backend/uploads/Form4_EndOfTerm1_2026.xlsx
@@ -445,162 +445,162 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SPP-F4-2026-016</v>
+        <v>SPP-F4-2026-006</v>
       </c>
       <c r="B2" t="str">
-        <v>Grace Mary Phiri</v>
+        <v>Blessings Nyirenda</v>
       </c>
       <c r="C2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>78</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J2">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SPP-F4-2026-017</v>
+        <v>SPP-F4-2026-007</v>
       </c>
       <c r="B3" t="str">
-        <v>Mphatso Banda</v>
+        <v>Limbani Peter Nyasulu</v>
       </c>
       <c r="C3">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E3">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="J3">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SPP-F4-2026-018</v>
+        <v>SPP-F4-2026-008</v>
       </c>
       <c r="B4" t="str">
-        <v>Chimwemwe Mkandawire</v>
+        <v>Pilirani Kachala</v>
       </c>
       <c r="C4">
+        <v>67</v>
+      </c>
+      <c r="D4">
+        <v>75</v>
+      </c>
+      <c r="E4">
+        <v>59</v>
+      </c>
+      <c r="F4">
+        <v>41</v>
+      </c>
+      <c r="G4">
+        <v>54</v>
+      </c>
+      <c r="H4">
+        <v>67</v>
+      </c>
+      <c r="I4">
         <v>55</v>
       </c>
-      <c r="D4">
-        <v>60</v>
-      </c>
-      <c r="E4">
-        <v>58</v>
-      </c>
-      <c r="F4">
-        <v>62</v>
-      </c>
-      <c r="G4">
-        <v>65</v>
-      </c>
-      <c r="H4">
-        <v>70</v>
-      </c>
-      <c r="I4">
-        <v>60</v>
-      </c>
       <c r="J4">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SPP-F4-2026-019</v>
+        <v>SPP-F4-2026-009</v>
       </c>
       <c r="B5" t="str">
-        <v>Tiyamike Gondwe</v>
+        <v>Ruth Esther Kalua</v>
       </c>
       <c r="C5">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H5">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SPP-F4-2026-020</v>
+        <v>SPP-F4-2026-010</v>
       </c>
       <c r="B6" t="str">
-        <v>Yankho Chirambo</v>
+        <v>Tamandani Precious Kamanga</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>52</v>
       </c>
       <c r="G6">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H6">
+        <v>56</v>
+      </c>
+      <c r="I6">
         <v>60</v>
       </c>
-      <c r="I6">
-        <v>50</v>
-      </c>
       <c r="J6">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/backend/uploads/Form4_EndOfTerm1_2026.xlsx
+++ b/backend/uploads/Form4_EndOfTerm1_2026.xlsx
@@ -445,10 +445,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SPP-F4-2026-006</v>
+        <v>SPP-F4-2026-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Blessings Nyirenda</v>
+        <v>Grace Mary Phiri</v>
       </c>
       <c r="C2">
         <v>94</v>
@@ -477,10 +477,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SPP-F4-2026-007</v>
+        <v>SPP-F4-2026-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Limbani Peter Nyasulu</v>
+        <v>Mphatso Banda</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -509,10 +509,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SPP-F4-2026-008</v>
+        <v>SPP-F4-2026-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Pilirani Kachala</v>
+        <v>Chimwemwe Mkandawire</v>
       </c>
       <c r="C4">
         <v>67</v>
@@ -541,10 +541,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SPP-F4-2026-009</v>
+        <v>SPP-F4-2026-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Ruth Esther Kalua</v>
+        <v>Tiyamike Gondwe</v>
       </c>
       <c r="C5">
         <v>44</v>
@@ -573,10 +573,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SPP-F4-2026-010</v>
+        <v>SPP-F4-2026-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Tamandani Precious Kamanga</v>
+        <v>Yankho Chirambo</v>
       </c>
       <c r="C6">
         <v>61</v>

--- a/backend/uploads/Form4_EndOfTerm1_2026.xlsx
+++ b/backend/uploads/Form4_EndOfTerm1_2026.xlsx
@@ -445,10 +445,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SPP-F4-2026-001</v>
+        <v>CSS-F4-2026-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Grace Mary Phiri</v>
+        <v>Thandiwe Ngoma</v>
       </c>
       <c r="C2">
         <v>94</v>
@@ -477,10 +477,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SPP-F4-2026-002</v>
+        <v>CSS-F4-2026-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Mphatso Banda</v>
+        <v>Tiyamike Ruth Chizuma</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -509,10 +509,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SPP-F4-2026-003</v>
+        <v>CSS-F4-2026-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Chimwemwe Mkandawire</v>
+        <v>Mavuto Chilenga</v>
       </c>
       <c r="C4">
         <v>67</v>
@@ -541,10 +541,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SPP-F4-2026-004</v>
+        <v>CSS-F4-2026-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Tiyamike Gondwe</v>
+        <v>Memory Grace Manda</v>
       </c>
       <c r="C5">
         <v>44</v>
@@ -573,10 +573,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SPP-F4-2026-005</v>
+        <v>CSS-F4-2026-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Yankho Chirambo</v>
+        <v>Dalitso Nkhata</v>
       </c>
       <c r="C6">
         <v>61</v>
